--- a/TC_Template (Gradution project) .xlsx
+++ b/TC_Template (Gradution project) .xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="945" uniqueCount="553">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -9454,6 +9454,21 @@
       <t xml:space="preserve"> 
  testingisfun99</t>
     </r>
+  </si>
+  <si>
+    <t>Environment</t>
+  </si>
+  <si>
+    <t>Browser: Chrome Version 146.0.3856.72 (Official build) (64-bit)
+OS: Windows 10</t>
+  </si>
+  <si>
+    <t>Browser: Chrome Version 146.0.3856.72 (Official build) (64-bit)
+OS: Windows 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
   </si>
 </sst>
 </file>
@@ -9659,7 +9674,7 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9691,18 +9706,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9722,18 +9725,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10166,7 +10157,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H128"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.8984375" style="8" customWidth="1"/>
@@ -10177,10 +10168,11 @@
     <col min="6" max="6" width="109.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="159.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.796875" style="2"/>
+    <col min="9" max="9" width="22.796875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.796875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="10" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="10" customFormat="1" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -10205,8 +10197,11 @@
       <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="10" t="s">
+        <v>549</v>
+      </c>
     </row>
-    <row r="2" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="110.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>8</v>
       </c>
@@ -10231,8 +10226,11 @@
       <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I2" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="3" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
@@ -10257,8 +10255,11 @@
       <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="I3" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>10</v>
       </c>
@@ -10283,8 +10284,11 @@
       <c r="H4" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I4" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>11</v>
       </c>
@@ -10309,8 +10313,11 @@
       <c r="H5" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I5" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>29</v>
       </c>
@@ -10335,8 +10342,11 @@
       <c r="H6" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I6" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="7" spans="1:8" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="55.2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>12</v>
       </c>
@@ -10361,8 +10371,11 @@
       <c r="H7" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I7" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="8" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>30</v>
       </c>
@@ -10387,8 +10400,11 @@
       <c r="H8" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I8" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="9" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>13</v>
       </c>
@@ -10413,8 +10429,11 @@
       <c r="H9" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I9" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="10" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>14</v>
       </c>
@@ -10439,8 +10458,11 @@
       <c r="H10" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I10" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="11" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
@@ -10465,8 +10487,11 @@
       <c r="H11" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I11" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="12" spans="1:8" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>16</v>
       </c>
@@ -10476,7 +10501,7 @@
       <c r="C12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="11" t="s">
         <v>70</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -10491,10 +10516,17 @@
       <c r="H12" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="I12" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="13" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="1:8" s="29" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="1:8" ht="124.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" spans="1:9" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
         <v>470</v>
       </c>
@@ -10519,12 +10551,15 @@
       <c r="H15" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I15" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="16" spans="1:8" ht="138" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="138" x14ac:dyDescent="0.25">
       <c r="A16" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="12" t="s">
         <v>78</v>
       </c>
       <c r="C16" s="5" t="s">
@@ -10545,8 +10580,11 @@
       <c r="H16" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I16" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="17" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
         <v>472</v>
       </c>
@@ -10571,8 +10609,11 @@
       <c r="H17" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I17" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="18" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
         <v>473</v>
       </c>
@@ -10597,8 +10638,11 @@
       <c r="H18" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I18" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="19" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
         <v>474</v>
       </c>
@@ -10623,8 +10667,11 @@
       <c r="H19" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I19" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="20" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>521</v>
       </c>
@@ -10649,8 +10696,11 @@
       <c r="H20" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I20" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="21" spans="1:8" ht="63" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="63" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
         <v>526</v>
       </c>
@@ -10675,21 +10725,24 @@
       <c r="H21" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I21" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="22" spans="1:8" s="13" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="17"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="24"/>
+    <row r="22" spans="1:9" s="20" customFormat="1" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="13"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="I22" s="15"/>
     </row>
-    <row r="23" spans="1:8" customFormat="1" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" customFormat="1" ht="66.599999999999994" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="16" t="s">
         <v>95</v>
       </c>
       <c r="C23" s="5" t="s">
@@ -10710,12 +10763,15 @@
       <c r="H23" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I23" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="24" spans="1:8" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" customFormat="1" ht="74.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="16" t="s">
         <v>103</v>
       </c>
       <c r="C24" s="5" t="s">
@@ -10736,18 +10792,22 @@
       <c r="H24" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I24" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="25" spans="1:8" s="21" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="13"/>
+    <row r="25" spans="1:9" s="17" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="20"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="15"/>
     </row>
-    <row r="26" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>109</v>
       </c>
@@ -10772,8 +10832,11 @@
       <c r="H26" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I26" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="27" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>104</v>
       </c>
@@ -10798,15 +10861,19 @@
       <c r="H27" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I27" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="28" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
+    <row r="28" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="I28" s="15"/>
     </row>
-    <row r="29" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>116</v>
       </c>
@@ -10831,8 +10898,11 @@
       <c r="H29" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I29" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="30" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>117</v>
       </c>
@@ -10857,8 +10927,11 @@
       <c r="H30" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I30" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="31" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>126</v>
       </c>
@@ -10883,15 +10956,19 @@
       <c r="H31" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I31" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="32" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
-      <c r="G32" s="19"/>
+    <row r="32" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="I32" s="15"/>
     </row>
-    <row r="33" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>131</v>
       </c>
@@ -10916,8 +10993,11 @@
       <c r="H33" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I33" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="34" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>138</v>
       </c>
@@ -10942,8 +11022,11 @@
       <c r="H34" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I34" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="35" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
         <v>143</v>
       </c>
@@ -10968,8 +11051,11 @@
       <c r="H35" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I35" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="36" spans="1:8" ht="138" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="138" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>144</v>
       </c>
@@ -10994,8 +11080,11 @@
       <c r="H36" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I36" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="37" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>145</v>
       </c>
@@ -11020,8 +11109,11 @@
       <c r="H37" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I37" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="38" spans="1:8" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="45.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
         <v>146</v>
       </c>
@@ -11046,8 +11138,11 @@
       <c r="H38" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I38" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="39" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
         <v>130</v>
       </c>
@@ -11072,8 +11167,11 @@
       <c r="H39" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I39" s="4" t="s">
+        <v>551</v>
+      </c>
     </row>
-    <row r="40" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>147</v>
       </c>
@@ -11098,8 +11196,11 @@
       <c r="H40" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I40" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="41" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>148</v>
       </c>
@@ -11124,8 +11225,11 @@
       <c r="H41" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I41" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="42" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>149</v>
       </c>
@@ -11150,10 +11254,17 @@
       <c r="H42" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I42" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="43" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="44" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I43" s="15"/>
+    </row>
+    <row r="44" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I44" s="15"/>
+    </row>
+    <row r="45" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>181</v>
       </c>
@@ -11178,8 +11289,11 @@
       <c r="H45" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I45" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="46" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>186</v>
       </c>
@@ -11204,8 +11318,11 @@
       <c r="H46" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I46" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="47" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>190</v>
       </c>
@@ -11230,8 +11347,11 @@
       <c r="H47" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I47" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="48" spans="1:8" ht="165.6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="165.6" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>195</v>
       </c>
@@ -11256,24 +11376,35 @@
       <c r="H48" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I48" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
+      <c r="I49" s="4"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
+      <c r="I50" s="4"/>
     </row>
-    <row r="51" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="1:8" s="28" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" s="20" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
+      <c r="I51" s="15" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I52" s="15"/>
+    </row>
+    <row r="53" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>196</v>
       </c>
@@ -11298,8 +11429,11 @@
       <c r="H53" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I53" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="54" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>200</v>
       </c>
@@ -11324,8 +11458,11 @@
       <c r="H54" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I54" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="55" spans="1:8" ht="138" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="138" x14ac:dyDescent="0.25">
       <c r="A55" s="8" t="s">
         <v>201</v>
       </c>
@@ -11350,8 +11487,11 @@
       <c r="H55" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I55" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="56" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>202</v>
       </c>
@@ -11376,8 +11516,11 @@
       <c r="H56" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I56" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="57" spans="1:8" ht="124.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="124.2" x14ac:dyDescent="0.25">
       <c r="A57" s="8" t="s">
         <v>203</v>
       </c>
@@ -11402,8 +11545,11 @@
       <c r="H57" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I57" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="58" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>204</v>
       </c>
@@ -11428,8 +11574,11 @@
       <c r="H58" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I58" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="59" spans="1:8" ht="165.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="165.6" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>205</v>
       </c>
@@ -11454,9 +11603,14 @@
       <c r="H59" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I59" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="60" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I60" s="15"/>
+    </row>
+    <row r="61" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>232</v>
       </c>
@@ -11481,8 +11635,11 @@
       <c r="H61" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I61" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="62" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>238</v>
       </c>
@@ -11507,8 +11664,11 @@
       <c r="H62" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I62" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="63" spans="1:8" ht="138" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="138" x14ac:dyDescent="0.25">
       <c r="A63" s="8" t="s">
         <v>239</v>
       </c>
@@ -11533,8 +11693,11 @@
       <c r="H63" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I63" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="64" spans="1:8" ht="138" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="138" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>245</v>
       </c>
@@ -11559,8 +11722,11 @@
       <c r="H64" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I64" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="65" spans="1:8" ht="165.6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="165.6" x14ac:dyDescent="0.25">
       <c r="A65" s="8" t="s">
         <v>250</v>
       </c>
@@ -11585,9 +11751,14 @@
       <c r="H65" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I65" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="66" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="67" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I66" s="15"/>
+    </row>
+    <row r="67" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A67" s="8" t="s">
         <v>256</v>
       </c>
@@ -11612,8 +11783,11 @@
       <c r="H67" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I67" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="68" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>262</v>
       </c>
@@ -11638,8 +11812,11 @@
       <c r="H68" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I68" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="69" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
         <v>263</v>
       </c>
@@ -11664,8 +11841,11 @@
       <c r="H69" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I69" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="70" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
         <v>264</v>
       </c>
@@ -11690,8 +11870,11 @@
       <c r="H70" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I70" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="71" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>274</v>
       </c>
@@ -11716,8 +11899,9 @@
       <c r="H71" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I71" s="4"/>
     </row>
-    <row r="72" spans="1:8" s="26" customFormat="1" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" s="18" customFormat="1" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>279</v>
       </c>
@@ -11739,12 +11923,17 @@
       <c r="G72" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="H72" s="26" t="s">
+      <c r="H72" s="18" t="s">
         <v>18</v>
       </c>
+      <c r="I72" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="73" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="1:8" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I73" s="15"/>
+    </row>
+    <row r="74" spans="1:9" ht="55.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>280</v>
       </c>
@@ -11769,8 +11958,11 @@
       <c r="H74" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I74" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="75" spans="1:8" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>282</v>
       </c>
@@ -11795,8 +11987,11 @@
       <c r="H75" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I75" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="76" spans="1:8" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="8" t="s">
         <v>283</v>
       </c>
@@ -11821,8 +12016,11 @@
       <c r="H76" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I76" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="77" spans="1:8" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="38.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>284</v>
       </c>
@@ -11847,8 +12045,11 @@
       <c r="H77" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I77" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="78" spans="1:8" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="46.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
         <v>285</v>
       </c>
@@ -11873,8 +12074,11 @@
       <c r="H78" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I78" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="79" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
         <v>286</v>
       </c>
@@ -11899,14 +12103,18 @@
       <c r="H79" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I79" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="80" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-      <c r="F80" s="19"/>
-      <c r="G80" s="19"/>
+    <row r="80" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D80" s="15"/>
+      <c r="E80" s="15"/>
+      <c r="F80" s="15"/>
+      <c r="G80" s="15"/>
+      <c r="I80" s="15"/>
     </row>
-    <row r="81" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
         <v>313</v>
       </c>
@@ -11931,8 +12139,11 @@
       <c r="H81" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I81" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="82" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
         <v>314</v>
       </c>
@@ -11957,8 +12168,11 @@
       <c r="H82" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I82" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="83" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A83" s="8" t="s">
         <v>315</v>
       </c>
@@ -11983,8 +12197,11 @@
       <c r="H83" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I83" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="84" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
         <v>316</v>
       </c>
@@ -12009,8 +12226,11 @@
       <c r="H84" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I84" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="85" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>317</v>
       </c>
@@ -12035,8 +12255,11 @@
       <c r="H85" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I85" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="86" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>318</v>
       </c>
@@ -12061,8 +12284,11 @@
       <c r="H86" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I86" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="87" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>305</v>
       </c>
@@ -12087,8 +12313,11 @@
       <c r="H87" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I87" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="88" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>309</v>
       </c>
@@ -12113,9 +12342,14 @@
       <c r="H88" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I88" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="89" spans="1:8" s="22" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I89" s="15"/>
+    </row>
+    <row r="90" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
         <v>343</v>
       </c>
@@ -12140,8 +12374,11 @@
       <c r="H90" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I90" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="91" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>344</v>
       </c>
@@ -12166,8 +12403,11 @@
       <c r="H91" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I91" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="92" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A92" s="8" t="s">
         <v>345</v>
       </c>
@@ -12192,8 +12432,11 @@
       <c r="H92" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I92" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="93" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
         <v>346</v>
       </c>
@@ -12218,8 +12461,11 @@
       <c r="H93" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I93" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="94" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A94" s="8" t="s">
         <v>347</v>
       </c>
@@ -12244,8 +12490,11 @@
       <c r="H94" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I94" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="95" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A95" s="8" t="s">
         <v>348</v>
       </c>
@@ -12270,8 +12519,11 @@
       <c r="H95" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I95" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="96" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A96" s="8" t="s">
         <v>349</v>
       </c>
@@ -12296,9 +12548,14 @@
       <c r="H96" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I96" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="97" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="98" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I97" s="15"/>
+    </row>
+    <row r="98" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>376</v>
       </c>
@@ -12323,8 +12580,11 @@
       <c r="H98" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I98" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="99" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>381</v>
       </c>
@@ -12349,8 +12609,11 @@
       <c r="H99" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I99" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="100" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>382</v>
       </c>
@@ -12375,8 +12638,11 @@
       <c r="H100" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I100" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="101" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>383</v>
       </c>
@@ -12401,8 +12667,11 @@
       <c r="H101" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I101" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="102" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>384</v>
       </c>
@@ -12427,8 +12696,11 @@
       <c r="H102" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I102" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="103" spans="1:8" ht="110.4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="110.4" x14ac:dyDescent="0.25">
       <c r="A103" s="8" t="s">
         <v>385</v>
       </c>
@@ -12453,9 +12725,14 @@
       <c r="H103" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I103" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="104" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="105" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I104" s="15"/>
+    </row>
+    <row r="105" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="8" t="s">
         <v>478</v>
       </c>
@@ -12480,8 +12757,11 @@
       <c r="H105" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I105" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="106" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="8" t="s">
         <v>479</v>
       </c>
@@ -12506,8 +12786,11 @@
       <c r="H106" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I106" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="107" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="8" t="s">
         <v>480</v>
       </c>
@@ -12532,8 +12815,11 @@
       <c r="H107" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I107" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="108" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="8" t="s">
         <v>481</v>
       </c>
@@ -12558,8 +12844,11 @@
       <c r="H108" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I108" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="109" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="8" t="s">
         <v>482</v>
       </c>
@@ -12584,8 +12873,11 @@
       <c r="H109" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I109" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="110" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="8" t="s">
         <v>475</v>
       </c>
@@ -12610,8 +12902,11 @@
       <c r="H110" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I110" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="111" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="8" t="s">
         <v>476</v>
       </c>
@@ -12636,8 +12931,11 @@
       <c r="H111" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I111" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="112" spans="1:8" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="49.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="8" t="s">
         <v>477</v>
       </c>
@@ -12662,9 +12960,14 @@
       <c r="H112" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I112" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="113" spans="1:8" s="24" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="114" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I113" s="15"/>
+    </row>
+    <row r="114" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A114" s="8" t="s">
         <v>406</v>
       </c>
@@ -12689,8 +12992,11 @@
       <c r="H114" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I114" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="115" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>410</v>
       </c>
@@ -12715,8 +13021,11 @@
       <c r="H115" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I115" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="116" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>411</v>
       </c>
@@ -12741,8 +13050,11 @@
       <c r="H116" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I116" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="117" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
         <v>412</v>
       </c>
@@ -12767,8 +13079,11 @@
       <c r="H117" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I117" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="118" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>413</v>
       </c>
@@ -12793,8 +13108,11 @@
       <c r="H118" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I118" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="119" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>430</v>
       </c>
@@ -12819,9 +13137,14 @@
       <c r="H119" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I119" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="120" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="121" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I120" s="15"/>
+    </row>
+    <row r="121" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>443</v>
       </c>
@@ -12846,8 +13169,11 @@
       <c r="H121" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I121" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="122" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A122" s="8" t="s">
         <v>444</v>
       </c>
@@ -12872,9 +13198,14 @@
       <c r="H122" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I122" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="123" spans="1:8" s="23" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="124" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I123" s="15"/>
+    </row>
+    <row r="124" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A124" s="8" t="s">
         <v>447</v>
       </c>
@@ -12899,8 +13230,11 @@
       <c r="H124" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="I124" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="125" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A125" s="8" t="s">
         <v>453</v>
       </c>
@@ -12925,8 +13259,11 @@
       <c r="H125" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I125" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="126" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A126" s="8" t="s">
         <v>454</v>
       </c>
@@ -12939,7 +13276,7 @@
       <c r="D126" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="E126" s="27" t="s">
+      <c r="E126" s="19" t="s">
         <v>464</v>
       </c>
       <c r="F126" s="4" t="s">
@@ -12951,8 +13288,11 @@
       <c r="H126" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I126" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="127" spans="1:8" ht="96.6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="96.6" x14ac:dyDescent="0.25">
       <c r="A127" s="8" t="s">
         <v>455</v>
       </c>
@@ -12977,14 +13317,12 @@
       <c r="H127" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="I127" s="4" t="s">
+        <v>550</v>
+      </c>
     </row>
-    <row r="128" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="128" spans="1:9" s="20" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A43:XFD44"/>
-    <mergeCell ref="A51:XFD52"/>
-    <mergeCell ref="A13:XFD14"/>
-  </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="H26:H42 H45:H50 H2:H12 H53:H71 H15:H24 H73:H1048576">
     <cfRule type="cellIs" dxfId="9" priority="19" operator="equal">
